--- a/data/trans_bre/P26-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P26-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 14,61</t>
+          <t>7,04; 14,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 12,96</t>
+          <t>4,06; 12,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 3,23</t>
+          <t>-5,33; 3,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 3,62</t>
+          <t>-4,1; 3,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,54; 73,91</t>
+          <t>28,98; 71,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 53,84</t>
+          <t>14,25; 50,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 15,97</t>
+          <t>-21,47; 14,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,33; 40,51</t>
+          <t>-28,76; 36,54</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,16</t>
+          <t>5,79; 12,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 10,65</t>
+          <t>4,19; 10,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 6,3</t>
+          <t>0,02; 5,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 3,31</t>
+          <t>-36,4; 3,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 41,11</t>
+          <t>16,34; 40,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,68; 30,29</t>
+          <t>10,7; 30,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 24,74</t>
+          <t>0,19; 22,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,0; 28,89</t>
+          <t>-78,09; 25,84</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 9,21</t>
+          <t>-3,07; 8,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 6,06</t>
+          <t>-7,13; 5,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 7,55</t>
+          <t>-2,96; 8,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 4,35</t>
+          <t>-3,36; 4,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 40,4</t>
+          <t>-10,67; 39,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 23,08</t>
+          <t>-21,38; 20,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 44,27</t>
+          <t>-12,69; 48,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 51,24</t>
+          <t>-26,83; 49,65</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,12</t>
+          <t>6,25; 10,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,24</t>
+          <t>3,35; 8,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,71</t>
+          <t>-0,58; 3,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 2,13</t>
+          <t>-27,6; 1,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,02; 40,75</t>
+          <t>20,94; 39,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 25,87</t>
+          <t>9,77; 25,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 15,36</t>
+          <t>-2,21; 16,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,68; 18,24</t>
+          <t>-71,98; 16,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P26-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P26-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-3,37%</t>
+          <t>-7,86%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 14,45</t>
+          <t>6,78; 14,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 12,06</t>
+          <t>4,29; 12,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 3,0</t>
+          <t>-5,73; 3,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,37</t>
+          <t>-5,04; 2,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,98; 71,57</t>
+          <t>27,57; 73,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,25; 50,4</t>
+          <t>15,16; 50,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 14,36</t>
+          <t>-22,45; 16,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 36,54</t>
+          <t>-32,87; 27,23</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,39</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-37,81%</t>
+          <t>31,62%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 12,7</t>
+          <t>5,86; 13,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,85</t>
+          <t>3,75; 10,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,76</t>
+          <t>0,09; 5,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,4; 3,06</t>
+          <t>1,34; 6,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 40,04</t>
+          <t>16,52; 40,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,7; 30,26</t>
+          <t>9,63; 30,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 22,26</t>
+          <t>0,18; 22,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,09; 25,84</t>
+          <t>9,43; 59,36</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 8,98</t>
+          <t>-2,77; 9,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 5,38</t>
+          <t>-6,77; 6,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 8,19</t>
+          <t>-3,17; 7,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,16</t>
+          <t>-3,23; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 39,95</t>
+          <t>-10,26; 39,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 20,67</t>
+          <t>-20,9; 24,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 48,54</t>
+          <t>-14,03; 43,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 49,65</t>
+          <t>-26,14; 53,5</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,65</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-30,5%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,93</t>
+          <t>6,1; 11,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,16</t>
+          <t>3,33; 8,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,94</t>
+          <t>-0,57; 3,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 1,87</t>
+          <t>0,4; 3,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,94; 39,62</t>
+          <t>20,41; 39,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 25,88</t>
+          <t>9,69; 26,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 16,26</t>
+          <t>-2,18; 15,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,98; 16,21</t>
+          <t>3,03; 35,71</t>
         </is>
       </c>
     </row>
